--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Library/AdminApp_Library_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Library/AdminApp_Library_tab_test_cases.xlsx
@@ -103,7 +103,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminSchoolLibrary | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminSchoolLibrary | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_LIBR_TC_3</t>
